--- a/Dia 11-Crear un Buscador/Buscar+hacia+la+Izquierda+sin+Buscarv+ni+Buscarx.xlsx
+++ b/Dia 11-Crear un Buscador/Buscar+hacia+la+Izquierda+sin+Buscarv+ni+Buscarx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GUSTAVO\Documents\Cursos Udemy\ExcelTotal\Dia 11-Crear un Buscador\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84CE966-A551-4CB6-A22A-EDABF9E45B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE0EC5B-CF46-4FD4-90AC-4A8E3BDB1348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{65CA577D-9EE9-4E76-A692-E68ECD1D3EEC}"/>
   </bookViews>
